--- a/tools/importer/reports/import-article-page.report.xlsx
+++ b/tools/importer/reports/import-article-page.report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="520" uniqueCount="313">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="318">
   <si>
     <t>_reportFile</t>
   </si>
@@ -262,13 +262,13 @@
     <t>ca/en/magazine.report.json</t>
   </si>
   <si>
-    <t>["columns","secure-teasers","secure-teasers","cards"]</t>
+    <t>["columns","secure-teasers","secure-teasers","recent-articles"]</t>
   </si>
   <si>
     <t>ca/en/magazine</t>
   </si>
   <si>
-    <t>2026-09-09T19:14:25.327Z</t>
+    <t>2026-09-17T17:39:08.223Z</t>
   </si>
   <si>
     <t>Magazine</t>
@@ -283,7 +283,7 @@
     <t>us/en/about-us</t>
   </si>
   <si>
-    <t>2026-09-08T20:47:50.809Z</t>
+    <t>2026-09-17T17:32:04.408Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/about-us.html</t>
@@ -319,7 +319,7 @@
     <t>us/en/magazine</t>
   </si>
   <si>
-    <t>2026-09-09T19:14:21.177Z</t>
+    <t>2026-09-17T17:39:02.819Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine.html</t>
@@ -884,6 +884,21 @@
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine/guide-la-skateparks.html</t>
+  </si>
+  <si>
+    <t>us/en/magazine/new-article.report.json</t>
+  </si>
+  <si>
+    <t>us/en/magazine/new-article</t>
+  </si>
+  <si>
+    <t>2026-09-17T18:18:31.122Z</t>
+  </si>
+  <si>
+    <t>Trail Running the Alps</t>
+  </si>
+  <si>
+    <t>https://wknd.site/us/en/magazine/new-article.html</t>
   </si>
   <si>
     <t>us/en/magazine/san-diego-surf.report.json</t>
@@ -1338,7 +1353,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H65"/>
+  <dimension ref="A1:H66"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="3" width="50" customWidth="1"/>
@@ -2928,21 +2943,21 @@
         <v>293</v>
       </c>
       <c r="G61" t="s">
-        <v>207</v>
+        <v>294</v>
       </c>
       <c r="H61" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B62" t="s">
         <v>188</v>
       </c>
       <c r="C62" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D62" t="s">
         <v>11</v>
@@ -2951,24 +2966,24 @@
         <v>190</v>
       </c>
       <c r="F62" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G62" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="H62" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B63" t="s">
         <v>188</v>
       </c>
       <c r="C63" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="D63" t="s">
         <v>11</v>
@@ -2977,24 +2992,24 @@
         <v>190</v>
       </c>
       <c r="F63" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="G63" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="H63" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B64" t="s">
         <v>188</v>
       </c>
       <c r="C64" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="D64" t="s">
         <v>11</v>
@@ -3003,10 +3018,10 @@
         <v>190</v>
       </c>
       <c r="F64" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="G64" t="s">
-        <v>306</v>
+        <v>217</v>
       </c>
       <c r="H64" t="s">
         <v>307</v>
@@ -3036,6 +3051,32 @@
       </c>
       <c r="H65" t="s">
         <v>312</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>313</v>
+      </c>
+      <c r="B66" t="s">
+        <v>188</v>
+      </c>
+      <c r="C66" t="s">
+        <v>314</v>
+      </c>
+      <c r="D66" t="s">
+        <v>11</v>
+      </c>
+      <c r="E66" t="s">
+        <v>190</v>
+      </c>
+      <c r="F66" t="s">
+        <v>315</v>
+      </c>
+      <c r="G66" t="s">
+        <v>316</v>
+      </c>
+      <c r="H66" t="s">
+        <v>317</v>
       </c>
     </row>
   </sheetData>
